--- a/Excel/Resource.xlsx
+++ b/Excel/Resource.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -33,6 +33,18 @@
   </si>
   <si>
     <t xml:space="preserve">/Script/Engine.Blueprint'/Game/Design/Weapon/WBP_Sword.WBP_Sword'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Script/Engine.AnimMontage'/Game/Characters/Lyra/Animation/Assets/Combat/PrimaryAttack_A_Slow_Montage.PrimaryAttack_A_Slow_Montage'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Script/Engine.AnimMontage'/Game/Characters/Lyra/Animation/Assets/Combat/PrimaryAttack_B_Slow_Montage.PrimaryAttack_B_Slow_Montage'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Script/Engine.AnimMontage'/Game/Characters/Lyra/Animation/Assets/Combat/PrimaryAttack_C_Slow_Montage.PrimaryAttack_C_Slow_Montage'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Script/Engine.AnimMontage'/Game/Characters/Lyra/Animation/Assets/Combat/PrimaryAttack_D_Slow_Montage.PrimaryAttack_D_Slow_Montage'</t>
   </si>
 </sst>
 </file>
@@ -345,7 +357,7 @@
   <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="61.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="120.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="36.7"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="9" style="1" width="8.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="10.58"/>
@@ -375,26 +387,42 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
